--- a/contractor_forms/007_project_change_order_form--contractor_forms.xlsx
+++ b/contractor_forms/007_project_change_order_form--contractor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,18 +520,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>project_change_order_form</t>
+          <t>project_details</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Project Change Order Form</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Project Details</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Provide project information</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,18 +547,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>project_change_order_form_uploaded_documents</t>
+          <t>change_details</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uploaded Documents</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Change Details</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Describe the project change</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,15 +574,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>project_change_order_form_change_details</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Change Details</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Documents</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Upload supporting documents</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -589,15 +601,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>project_change_order_form_collect_e_signature</t>
+          <t>collect_e_signature</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Collect E-Signature</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>E-Signature Collection</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Collect electronic signatures</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -612,7 +628,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>project_change_order_form_contractor_forms</t>
+          <t>contractor_forms</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -620,10 +636,14 @@
           <t>Contractor Forms</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Select contractor forms</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,87 +655,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>project_change_order_form_uploaded_documents</t>
+          <t>review_and_submit</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uploaded Documents</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Review and Submit</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Confirm submission</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>project_change_order_form_change_details</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Change Details</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>project_change_order_form_collect_e_signature</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Collect E-Signature</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>project_change_order_form_contractor_forms</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Contractor Forms</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -730,12 +685,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -758,202 +713,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>project_change_order_form_collect_e_signature_choices</t>
+          <t>collect_e_signature_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>project_change_order_form_collect_e_signature_choices</t>
+          <t>collect_e_signature_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>project_change_order_form_collect_e_signature_choices</t>
+          <t>contractor_forms_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>form_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Form 1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>project_change_order_form_contractor_forms_choices</t>
+          <t>contractor_forms_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>form_1</t>
+          <t>form_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Form 1</t>
+          <t>Form 2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>project_change_order_form_contractor_forms_choices</t>
+          <t>contractor_forms_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>form_2</t>
+          <t>form_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
-        <is>
-          <t>Form 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>project_change_order_form_contractor_forms_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>form_3</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Form 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>project_change_order_form_collect_e_signature_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>project_change_order_form_collect_e_signature_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>project_change_order_form_collect_e_signature_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>project_change_order_form_contractor_forms_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>form_1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Form 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>project_change_order_form_contractor_forms_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>form_2</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Form 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>project_change_order_form_contractor_forms_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>form_3</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
         <is>
           <t>Form 3</t>
         </is>
